--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 42 clubs short</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10933,8 +10933,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11789,7 +11789,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3288,7 +3292,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3389,7 +3397,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3902,7 +3914,11 @@
       <c r="AB31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4003,7 +4019,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4205,7 +4225,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4920,7 +4944,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5223,7 +5251,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5837,7 +5869,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6043,7 +6079,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6655,7 +6695,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -7063,7 +7107,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 42 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="10" t="n">
         <v>2</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7098,8 +7098,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>1</v>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="9" t="n">
         <v>0</v>
@@ -11540,7 +11540,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2433,8 +2433,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P17" s="9" t="n">
-        <v>3</v>
+      <c r="P17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2673,8 +2673,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2774,8 +2774,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2980,8 +2980,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3051,8 +3051,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P23" s="9" t="n">
-        <v>3</v>
+      <c r="P23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3361,8 +3361,8 @@
       <c r="P26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" s="9" t="n">
-        <v>1</v>
+      <c r="Q26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3370,8 +3370,8 @@
       <c r="S26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T26" s="9" t="n">
-        <v>0</v>
+      <c r="T26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="9" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -4010,8 +4010,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>2</v>
@@ -4204,11 +4204,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>3</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4523,8 +4523,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5186,13 +5186,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5230,8 +5230,8 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>1</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5553,8 +5553,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="P50" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6119,13 +6119,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>UNICEF Toastmasters Club</t>
+          <t>UN House Nepal Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6892,8 +6892,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V61" s="9" t="n">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7611,8 +7611,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7813,8 +7813,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7912,8 +7912,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -8011,8 +8011,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9044,13 +9044,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9100,8 +9100,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9341,13 +9341,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9397,8 +9397,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9418,15 +9418,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7873333</v>
+        <v>4497510</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>BD Oasis Toastmasters Club</t>
+          <t>DHAKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9440,17 +9440,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9478,26 +9478,26 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>0</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9517,15 +9517,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>4497510</v>
+        <v>7301075</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>DHAKA TOASTMASTERS CLUB</t>
+          <t>FCI Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9539,17 +9539,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9577,26 +9577,26 @@
       <c r="S87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="10" t="n">
-        <v>1</v>
+      <c r="T87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="10" t="n">
-        <v>4</v>
+      <c r="V87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="10" t="n">
-        <v>1</v>
+      <c r="Z87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9616,11 +9616,11 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>7301075</v>
+        <v>7873333</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>FCI Toastmasters Club</t>
+          <t>Limitless Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0</v>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9793,8 +9793,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10119,7 +10119,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10189,8 +10189,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10565,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" s="10" t="n">
         <v>1</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10684,8 +10684,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10981,8 +10981,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="10" t="n">
-        <v>1</v>
+      <c r="Z101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11078,7 +11078,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11210,7 +11210,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -11243,7 +11243,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11309,7 +11309,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11507,7 +11507,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11573,7 +11573,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11606,7 +11606,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -11705,7 +11705,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1167,17 +1167,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1223,8 +1223,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1272,17 +1272,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1316,11 +1316,11 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1373,17 +1373,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1478,17 +1478,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1894,17 +1894,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2302,17 +2302,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2451,8 +2451,8 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>3</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2556,11 +2556,11 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>0</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>6</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2819,17 +2819,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2855,13 +2855,13 @@
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2924,13 +2924,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2962,14 +2962,14 @@
       <c r="S22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3025,17 +3025,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3081,8 +3081,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3126,13 +3126,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3271,8 +3271,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="10" t="n">
         <v>2</v>
@@ -3437,17 +3437,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3647,13 +3647,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3748,17 +3748,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3804,8 +3804,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3849,17 +3849,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3983,11 +3983,11 @@
       <c r="P32" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q32" s="9" t="n">
-        <v>1</v>
+      <c r="Q32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="9" t="n">
         <v>1</v>
@@ -3998,8 +3998,8 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>0</v>
+      <c r="V32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4059,13 +4059,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4568,17 +4568,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4673,13 +4673,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5186,13 +5186,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5291,13 +5291,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="9" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5436,8 +5436,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>0</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5598,17 +5598,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5909,17 +5909,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6119,17 +6119,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6163,11 +6163,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>3</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>6</v>
@@ -6220,17 +6220,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6674,8 +6674,8 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>2</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6735,17 +6735,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6779,8 +6779,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>2</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6836,17 +6836,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6937,17 +6937,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V61" s="9" t="n">
         <v>1</v>
@@ -7042,17 +7042,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7396,8 +7396,8 @@
       <c r="V65" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W65" s="9" t="n">
-        <v>3</v>
+      <c r="W65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X65" s="10" t="n">
         <v>7</v>
@@ -7454,17 +7454,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7599,8 +7599,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>2</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7955,13 +7955,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -8000,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8197,8 +8197,8 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>1</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8252,13 +8252,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>7</v>
@@ -8351,17 +8351,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8396,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8549,13 +8549,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8648,13 +8648,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9044,13 +9044,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9143,17 +9143,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9341,13 +9341,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9440,13 +9440,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9481,14 +9481,14 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W86" s="9" t="n">
-        <v>1</v>
+      <c r="W86" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>6</v>
@@ -9539,13 +9539,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9737,13 +9737,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>1</v>
@@ -9781,11 +9781,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9822,7 +9822,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9880,11 +9880,11 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>6</v>
@@ -9913,15 +9913,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>7672606</v>
+        <v>28680926</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Dhaka North Toastmasters Club</t>
+          <t>Credence Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9935,17 +9935,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9980,19 +9980,19 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="10" t="n">
-        <v>6</v>
+      <c r="X91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="10" t="n">
-        <v>1</v>
+      <c r="Z91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10012,15 +10012,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>6826688</v>
+        <v>7672606</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Independent University Bangladesh Toastmasters Club</t>
+          <t>Dhaka North Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10034,13 +10034,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10078,20 +10078,20 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10111,15 +10111,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>28675774</v>
+        <v>6826688</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Uttara Speakers Toastmasters Club</t>
+          <t>Independent University Bangladesh Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10184,13 +10184,13 @@
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="10" t="n">
-        <v>1</v>
+      <c r="Z93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10206,19 +10206,19 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7550630</v>
+        <v>28675774</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>100X Toastmasters Club</t>
+          <t>Uttara Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -10276,14 +10276,14 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
+      <c r="V94" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W94" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W94" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X94" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10309,11 +10309,11 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28680418</v>
+        <v>7550630</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Dhanmondi Leaders Toastmasters</t>
+          <t>100X Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -10331,17 +10331,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="9" t="n">
         <v>0</v>
@@ -10379,10 +10379,10 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -10408,15 +10408,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>7888866</v>
+        <v>28680418</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Dhrupodi Bangla Toastmasters Club</t>
+          <t>Dhanmondi Leaders Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10430,17 +10430,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10474,20 +10474,20 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10507,15 +10507,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28678391</v>
+        <v>7888866</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Nifty Toastmasters Club</t>
+          <t>Dhrupodi Bangla Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10529,13 +10529,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10556,22 +10556,22 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S97" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="n">
-        <v>1</v>
+      <c r="S97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
         <v>2</v>
@@ -10580,13 +10580,13 @@
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10602,19 +10602,19 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28676515</v>
+        <v>28678391</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>ACCA Bangladesh Toastmasters Club</t>
+          <t>Nifty Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10628,13 +10628,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10655,25 +10655,25 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
+      <c r="S98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10705,15 +10705,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>7472687</v>
+        <v>28676515</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Bangladesh Youth Toastmasters Club</t>
+          <t>ACCA Bangladesh Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10730,10 +10730,10 @@
         <v>10</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10771,14 +10771,14 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10804,15 +10804,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>6976970</v>
+        <v>7472687</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Mastermind Toastmasters</t>
+          <t>Bangladesh Youth Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10871,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10882,8 +10882,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10903,11 +10903,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28680557</v>
+        <v>6976970</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Nexus Toastmasters Club</t>
+          <t>Mastermind Toastmasters</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -10925,17 +10925,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10970,13 +10970,13 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -10990,8 +10990,107 @@
       <c r="AB101" s="4" t="n"/>
       <c r="AC101" s="4" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>28680557</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Nexus Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="4" t="n"/>
+      <c r="AC102" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC101"/>
+  <autoFilter ref="A1:AC102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11078,7 +11177,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11093,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -11126,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -11159,7 +11258,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -11177,7 +11276,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11192,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -11210,13 +11309,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -11243,13 +11342,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -11258,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11276,7 +11375,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11291,7 +11390,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -11309,7 +11408,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11357,7 +11456,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -11408,7 +11507,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11456,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -11474,7 +11573,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11489,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -11507,7 +11606,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11522,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -11555,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -11573,7 +11672,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11588,7 +11687,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -11639,7 +11738,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -11654,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -11720,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -11738,13 +11837,13 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -11768,16 +11867,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -11786,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -11804,7 +11903,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11837,7 +11936,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1167,17 +1167,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2445,8 +2445,8 @@
       <c r="S17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>1</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4923,11 +4923,11 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>0</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>7</v>
@@ -5834,7 +5834,7 @@
         <v>5</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="U52" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52" s="9" t="n">
         <v>1</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -8648,13 +8648,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10061,22 +10061,22 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
         <v>4</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10232,13 +10232,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10279,8 +10279,8 @@
       <c r="V94" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W94" s="9" t="n">
-        <v>2</v>
+      <c r="W94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>6</v>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10361,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10369,8 +10369,8 @@
       <c r="S95" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
@@ -11192,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -11276,7 +11276,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11870,13 +11870,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -11903,7 +11903,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/41/inyear.xlsx
+++ b/docs/d/41/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -9146,10 +9146,10 @@
         <v>16</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10331,13 +10331,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10378,8 +10378,8 @@
       <c r="V95" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>3</v>
+      <c r="W95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>5</v>
@@ -11903,7 +11903,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
